--- a/finanzas-master.xlsx
+++ b/finanzas-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\japaricio\Dropbox\Cuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751B3423-5E86-4C42-81A6-97BD3E9B57D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD129F8-DAA7-4D05-86B6-651C36FECE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1682,7 +1682,7 @@
         <v>71</v>
       </c>
       <c r="E21" s="5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F21" s="15">
         <v>2026</v>
@@ -1715,7 +1715,7 @@
         <v>73</v>
       </c>
       <c r="E22" s="7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F22" s="18">
         <v>2026</v>

--- a/finanzas-master.xlsx
+++ b/finanzas-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\japaricio\Dropbox\Cuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD129F8-DAA7-4D05-86B6-651C36FECE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C3E59F-0014-4E98-91E1-4AE412F8B984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1528,7 +1528,7 @@
         <v>2026</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>129</v>
@@ -2611,32 +2611,32 @@
     <mergeCell ref="A9:K9"/>
     <mergeCell ref="A47:K47"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:K2 A3 A9 A10:K46 A47 A48:K509 A4:K8">
+  <conditionalFormatting sqref="A2:K2 A3 A9 A47 A48:K509 A4:K8 A10:K46">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($A2&lt;&gt;"",$B2&lt;&gt;"",$J2=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" sqref="B2 B48:B509 B10:B46 B7:B8 B4:B6" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2 B48:B509 B10:B46 B4:B8" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"ingreso,gasto"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2 C48:C509 C10:C46 C7:C8 C4:C6" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2 C48:C509 C10:C46 C4:C8" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"ingresosFijos,ingresosBonus,gastosFijos,gastosVacaciones"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2 G48:G509 G10:G46 G7:G8 G4:G6" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2 G48:G509 G4:G8 G10:G46" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"mensual,anual"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I2 I48:I509 I10:I46 I7:I8 I4:I6" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I2 I48:I509 I10:I46 I4:I8" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"cuenta,tarjeta"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2 J48:J509 J10:J46 J7:J8 J4:J6" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2 J48:J509 J10:J46 J4:J8" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" sqref="F2 F48:F509 F10:F46 F7:F8 F4:F6" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="whole" allowBlank="1" sqref="F2 F48:F509 F10:F46 F4:F8" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>2024</formula1>
       <formula2>2040</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" sqref="K2 K48:K509 K10:K46 K7:K8 K4:K6" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="whole" allowBlank="1" sqref="K2 K48:K509 K10:K46 K4:K8" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>1</formula1>
       <formula2>9999</formula2>
     </dataValidation>

--- a/finanzas-master.xlsx
+++ b/finanzas-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\japaricio\Dropbox\Cuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C3E59F-0014-4E98-91E1-4AE412F8B984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9066F170-F09F-4C24-9128-CCDC1DF47EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2263,7 +2263,7 @@
         <v>58</v>
       </c>
       <c r="E40" s="7">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F40" s="18">
         <v>2026</v>

--- a/finanzas-master.xlsx
+++ b/finanzas-master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10320"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\japaricio\Dropbox\Cuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9066F170-F09F-4C24-9128-CCDC1DF47EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA550BE-1A3E-4B03-A767-005D4C7513C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MASTER!$A$1:$K$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1175,22 +1175,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22" style="2" customWidth="1"/>
-    <col min="4" max="4" width="27" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14" style="2" customWidth="1"/>
-    <col min="8" max="8" width="28.44140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13" style="2" customWidth="1"/>
-    <col min="10" max="11" width="10" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="27.98046875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.97265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.05859375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.0390625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.9296875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.02734375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.98828125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="28.3828125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.046875" style="2" customWidth="1"/>
+    <col min="10" max="11" width="9.953125" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1225,8 +1225,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="4.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="25" t="s">
         <v>11</v>
       </c>
@@ -1241,7 +1241,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="25"/>
     </row>
-    <row r="4" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>12</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>23</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>18</v>
       </c>
@@ -1344,9 +1344,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="26" t="s">
         <v>26</v>
       </c>
@@ -1361,7 +1361,7 @@
       <c r="J9" s="26"/>
       <c r="K9" s="26"/>
     </row>
-    <row r="10" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>40</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
         <v>125</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="21"/>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -1440,7 +1440,7 @@
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>37</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
         <v>35</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>127</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
         <v>33</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="21"/>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -1589,7 +1589,7 @@
       <c r="J17" s="22"/>
       <c r="K17" s="22"/>
     </row>
-    <row r="18" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
         <v>27</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
         <v>31</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="21"/>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -1668,7 +1668,7 @@
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
     </row>
-    <row r="21" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
         <v>70</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
         <v>76</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="14" t="s">
         <v>78</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
         <v>82</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="14" t="s">
         <v>74</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="13" t="s">
         <v>48</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
         <v>51</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="13" t="s">
         <v>60</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="21"/>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
@@ -1982,7 +1982,7 @@
       <c r="J30" s="22"/>
       <c r="K30" s="22"/>
     </row>
-    <row r="31" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="13" t="s">
         <v>42</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="14" t="s">
         <v>45</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -2063,7 +2063,7 @@
       <c r="J33" s="22"/>
       <c r="K33" s="22"/>
     </row>
-    <row r="34" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="13" t="s">
         <v>63</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="14" t="s">
         <v>65</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="13" t="s">
         <v>68</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="14" t="s">
         <v>80</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
@@ -2214,7 +2214,7 @@
       <c r="J38" s="22"/>
       <c r="K38" s="22"/>
     </row>
-    <row r="39" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="13" t="s">
         <v>52</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="14" t="s">
         <v>57</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="13" t="s">
         <v>54</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="21"/>
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
@@ -2332,7 +2332,7 @@
       <c r="J42" s="22"/>
       <c r="K42" s="22"/>
     </row>
-    <row r="43" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="13" t="s">
         <v>84</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="14" t="s">
         <v>87</v>
       </c>
@@ -2402,11 +2402,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="27" t="s">
         <v>89</v>
       </c>
@@ -2421,7 +2421,7 @@
       <c r="J47" s="27"/>
       <c r="K47" s="27"/>
     </row>
-    <row r="48" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="13" t="s">
         <v>90</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>93</v>
       </c>
       <c r="I48" s="16" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="J48" s="15">
         <v>1</v>
@@ -2456,7 +2456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="14" t="s">
         <v>94</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>96</v>
       </c>
       <c r="I49" s="19" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="J49" s="18">
         <v>1</v>
@@ -2491,7 +2491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="13" t="s">
         <v>97</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>99</v>
       </c>
       <c r="I50" s="16" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="J50" s="15">
         <v>1</v>
@@ -2526,7 +2526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="14" t="s">
         <v>100</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>67</v>
       </c>
       <c r="I51" s="19" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="J51" s="18">
         <v>1</v>
@@ -2561,7 +2561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="13" t="s">
         <v>102</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>104</v>
       </c>
       <c r="I52" s="16" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="J52" s="15">
         <v>1</v>
@@ -2596,13 +2596,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E55" s="3"/>
     </row>
   </sheetData>
@@ -2611,7 +2611,7 @@
     <mergeCell ref="A9:K9"/>
     <mergeCell ref="A47:K47"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:K2 A3 A9 A47 A48:K509 A4:K8 A10:K46">
+  <conditionalFormatting sqref="A2:K2 A3 A4:K8 A9 A10:K46 A47 A48:K509">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($A2&lt;&gt;"",$B2&lt;&gt;"",$J2=0)</formula>
     </cfRule>
@@ -2653,21 +2653,21 @@
     <tabColor rgb="FF7C3AED"/>
   </sheetPr>
   <dimension ref="B2:C15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3" style="11" customWidth="1"/>
-    <col min="2" max="2" width="31" style="11" customWidth="1"/>
-    <col min="3" max="3" width="109.88671875" style="11" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="11"/>
+    <col min="1" max="1" width="2.95703125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="30.9375" style="11" customWidth="1"/>
+    <col min="3" max="3" width="109.90625" style="11" customWidth="1"/>
+    <col min="4" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="28" t="s">
         <v>105</v>
       </c>
       <c r="C2" s="29"/>
     </row>
-    <row r="4" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="10" t="s">
         <v>106</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="10" t="s">
         <v>108</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="10" t="s">
         <v>110</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="10" t="s">
         <v>112</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="10" t="s">
         <v>114</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="10" t="s">
         <v>116</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="10" t="s">
         <v>118</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="10" t="s">
         <v>120</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="10" t="s">
         <v>122</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="30" t="s">
         <v>124</v>
       </c>
